--- a/results/0916-all/闽南粤中农林水产区/tech_selected_summary.xlsx
+++ b/results/0916-all/闽南粤中农林水产区/tech_selected_summary.xlsx
@@ -391,289 +391,289 @@
     <t>紫金县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>技术82</t>
-  </si>
-  <si>
-    <t>技术83</t>
-  </si>
-  <si>
-    <t>技术84</t>
-  </si>
-  <si>
-    <t>技术85</t>
-  </si>
-  <si>
-    <t>技术86</t>
-  </si>
-  <si>
-    <t>技术87</t>
-  </si>
-  <si>
-    <t>技术88</t>
-  </si>
-  <si>
-    <t>技术89</t>
-  </si>
-  <si>
-    <t>技术90</t>
-  </si>
-  <si>
-    <t>技术91</t>
-  </si>
-  <si>
-    <t>技术92</t>
-  </si>
-  <si>
-    <t>技术93</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Tech82</t>
+  </si>
+  <si>
+    <t>Tech83</t>
+  </si>
+  <si>
+    <t>Tech84</t>
+  </si>
+  <si>
+    <t>Tech85</t>
+  </si>
+  <si>
+    <t>Tech86</t>
+  </si>
+  <si>
+    <t>Tech87</t>
+  </si>
+  <si>
+    <t>Tech88</t>
+  </si>
+  <si>
+    <t>Tech89</t>
+  </si>
+  <si>
+    <t>Tech90</t>
+  </si>
+  <si>
+    <t>Tech91</t>
+  </si>
+  <si>
+    <t>Tech92</t>
+  </si>
+  <si>
+    <t>Tech93</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -796,10 +796,10 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 333466992.48</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>333466992.48</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -826,7 +826,7 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 702746209.51</t>
+    <t>702746209.51</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -862,7 +862,7 @@
     <t>EEF(NI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 129577907.90</t>
+    <t>129577907.90</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -889,7 +889,7 @@
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 291278138.16</t>
+    <t>291278138.16</t>
   </si>
   <si>
     <t>Biochar_dairy</t>
@@ -901,10 +901,10 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 298670925.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 23302700.12</t>
+    <t>298670925.62</t>
+  </si>
+  <si>
+    <t>23302700.12</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -913,25 +913,25 @@
     <t>Frequent removal_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 333506982.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 226947712.26</t>
+    <t>333506982.33</t>
+  </si>
+  <si>
+    <t>226947712.26</t>
   </si>
   <si>
     <t>compost（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 444801095.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 3191775.90</t>
+    <t>444801095.79</t>
+  </si>
+  <si>
+    <t>3191775.90</t>
   </si>
   <si>
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 241806487.11</t>
+    <t>241806487.11</t>
   </si>
   <si>
     <t>Urease Inhibitor_beef cattle</t>
@@ -940,13 +940,13 @@
     <t>Chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 114602327.93</t>
+    <t>114602327.93</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 314041491.15</t>
+    <t>314041491.15</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -961,7 +961,7 @@
     <t>Frequent removal_pig</t>
   </si>
   <si>
-    <t>总经济成本: 27188472.75</t>
+    <t>27188472.75</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -976,7 +976,7 @@
     <t>manure（low）≤30%_friut</t>
   </si>
   <si>
-    <t>总经济成本: 605508667.41</t>
+    <t>605508667.41</t>
   </si>
   <si>
     <t>Low protein diet_poultry</t>
@@ -1045,7 +1045,7 @@
     <t>irrigation (drip irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 856817195.38</t>
+    <t>856817195.38</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
@@ -1054,13 +1054,13 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 171088783.93</t>
+    <t>171088783.93</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 207399532.59</t>
+    <t>207399532.59</t>
   </si>
   <si>
     <t>metal salt_Poultry</t>
@@ -1072,19 +1072,19 @@
     <t>Bioflilter_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 892688915.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 4565041.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 194778619.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 256030954.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 35627.50</t>
+    <t>892688915.37</t>
+  </si>
+  <si>
+    <t>4565041.51</t>
+  </si>
+  <si>
+    <t>194778619.04</t>
+  </si>
+  <si>
+    <t>256030954.84</t>
+  </si>
+  <si>
+    <t>35627.50</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -1102,13 +1102,13 @@
     <t>manure（high）≥70%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 341030047.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 155614680.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 42721529.18</t>
+    <t>341030047.45</t>
+  </si>
+  <si>
+    <t>155614680.98</t>
+  </si>
+  <si>
+    <t>42721529.18</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
@@ -1138,19 +1138,19 @@
     <t>tillage management (reduced tillage)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 178950805.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 190172356.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 388470541.45</t>
+    <t>178950805.72</t>
+  </si>
+  <si>
+    <t>190172356.85</t>
+  </si>
+  <si>
+    <t>388470541.45</t>
   </si>
   <si>
     <t>Cover_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 326473386.45</t>
+    <t>326473386.45</t>
   </si>
   <si>
     <t>Composting_pig</t>
@@ -1159,10 +1159,10 @@
     <t>Mixture additives _pig</t>
   </si>
   <si>
-    <t>总经济成本: 145321519.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 144933205.12</t>
+    <t>145321519.87</t>
+  </si>
+  <si>
+    <t>144933205.12</t>
   </si>
   <si>
     <t>4R(Right place)_vegetable</t>
@@ -1171,7 +1171,7 @@
     <t>cover crop (non-leguminous)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 452570066.57</t>
+    <t>452570066.57</t>
   </si>
   <si>
     <t>Physical additives_pig</t>
@@ -1183,10 +1183,10 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 81439078.17</t>
-  </si>
-  <si>
-    <t>总经济成本: 863701313.27</t>
+    <t>81439078.17</t>
+  </si>
+  <si>
+    <t>863701313.27</t>
   </si>
   <si>
     <t>EEF(NI)_wheat</t>
@@ -1201,13 +1201,13 @@
     <t>4R(Right place)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 117242961.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 199234903.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 170954057.00</t>
+    <t>117242961.66</t>
+  </si>
+  <si>
+    <t>199234903.35</t>
+  </si>
+  <si>
+    <t>170954057.00</t>
   </si>
   <si>
     <t>surface crust cover_dairy</t>
@@ -1243,103 +1243,103 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 1268016922.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 506893517.45</t>
+    <t>1268016922.90</t>
+  </si>
+  <si>
+    <t>506893517.45</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 298448492.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 783093631.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 165379909.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 652024009.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 328331547.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 652041478.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 440869598.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 390778664.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 123462755.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 39982023.27</t>
-  </si>
-  <si>
-    <t>总经济成本: 1619736.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 14184457.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 911241113.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 119775403.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 76185125.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 358483279.66</t>
+    <t>298448492.33</t>
+  </si>
+  <si>
+    <t>783093631.41</t>
+  </si>
+  <si>
+    <t>165379909.77</t>
+  </si>
+  <si>
+    <t>652024009.19</t>
+  </si>
+  <si>
+    <t>328331547.26</t>
+  </si>
+  <si>
+    <t>652041478.25</t>
+  </si>
+  <si>
+    <t>440869598.86</t>
+  </si>
+  <si>
+    <t>390778664.77</t>
+  </si>
+  <si>
+    <t>123462755.24</t>
+  </si>
+  <si>
+    <t>39982023.27</t>
+  </si>
+  <si>
+    <t>1619736.99</t>
+  </si>
+  <si>
+    <t>14184457.36</t>
+  </si>
+  <si>
+    <t>911241113.22</t>
+  </si>
+  <si>
+    <t>119775403.57</t>
+  </si>
+  <si>
+    <t>76185125.32</t>
+  </si>
+  <si>
+    <t>358483279.66</t>
   </si>
   <si>
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 1483350896.87</t>
+    <t>1483350896.87</t>
   </si>
   <si>
     <t>surface crust cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 24696185.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 611127874.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 395871273.93</t>
-  </si>
-  <si>
-    <t>总经济成本: 108240790.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 361273527.90</t>
+    <t>24696185.79</t>
+  </si>
+  <si>
+    <t>611127874.28</t>
+  </si>
+  <si>
+    <t>395871273.93</t>
+  </si>
+  <si>
+    <t>108240790.38</t>
+  </si>
+  <si>
+    <t>361273527.90</t>
   </si>
   <si>
     <t>Tannins_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 259001249.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 109665545.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 112299134.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 26931921.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 480399839.78</t>
+    <t>259001249.59</t>
+  </si>
+  <si>
+    <t>109665545.49</t>
+  </si>
+  <si>
+    <t>112299134.87</t>
+  </si>
+  <si>
+    <t>26931921.31</t>
+  </si>
+  <si>
+    <t>480399839.78</t>
   </si>
 </sst>
 </file>
